--- a/ig/DM-MARS-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00.000+00:00</t>
+    <t>2026-03-30T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="937">
   <si>
     <t>Property</t>
   </si>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>428</t>
+    <t>429</t>
   </si>
   <si>
     <t>Code</t>
@@ -2819,6 +2819,12 @@
   </si>
   <si>
     <t>Points locaux d'information dédiés aux personnes âgées. Ces services peuvent être rattachés à des CCAS ( Centre Communaux d'Action Sociale)</t>
+  </si>
+  <si>
+    <t>705</t>
+  </si>
+  <si>
+    <t>Groupe d’Entraide Mutuelle (GEM)</t>
   </si>
 </sst>
 </file>
@@ -3336,7 +3342,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D429"/>
+  <dimension ref="A1:D430"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -8505,6 +8511,20 @@
         <v>934</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B430" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="C430" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="D430" t="s" s="2">
+        <v>925</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
